--- a/artfynd/A 20695-2025 artfynd.xlsx
+++ b/artfynd/A 20695-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325502</v>
+        <v>123325511</v>
       </c>
       <c r="B2" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600409</v>
+        <v>600380</v>
       </c>
       <c r="R2" t="n">
-        <v>6973389</v>
+        <v>6973433</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1465</t>
+          <t>2024_1460</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vid myr</t>
+          <t>Produktionsskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,37 +805,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325495</v>
+        <v>123325529</v>
       </c>
       <c r="B3" t="n">
-        <v>79904</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600426</v>
+        <v>600362</v>
       </c>
       <c r="R3" t="n">
-        <v>6973743</v>
+        <v>6973711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1469</t>
+          <t>2024_1450</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,15 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325529</v>
+        <v>123325526</v>
       </c>
       <c r="B4" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -989,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600362</v>
+        <v>600376</v>
       </c>
       <c r="R4" t="n">
-        <v>6973711</v>
+        <v>6973693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1450</t>
+          <t>2024_1452</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1029,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Brandstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,37 +1065,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325526</v>
+        <v>123325495</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1124,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600376</v>
+        <v>600426</v>
       </c>
       <c r="R5" t="n">
-        <v>6973693</v>
+        <v>6973743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1139,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1452</t>
+          <t>2024_1469</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1164,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,12 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,7 +1179,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1210,15 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325499</v>
+        <v>123325505</v>
       </c>
       <c r="B6" t="n">
-        <v>98100</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,31 +1201,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1259,10 +1234,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600396</v>
+        <v>600394</v>
       </c>
       <c r="R6" t="n">
-        <v>6973386</v>
+        <v>6973397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1264,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1467</t>
+          <t>2024_1463</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1299,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1284,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vid myr</t>
+          <t>vid myr</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1345,37 +1320,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325527</v>
+        <v>123325502</v>
       </c>
       <c r="B7" t="n">
-        <v>79377</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1385,7 +1355,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1364,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600373</v>
+        <v>600409</v>
       </c>
       <c r="R7" t="n">
-        <v>6973646</v>
+        <v>6973389</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1394,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1451</t>
+          <t>2024_1465</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,12 +1414,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Vid myr</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1480,47 +1450,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123434993</v>
+        <v>123325499</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1529,10 +1494,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600451</v>
+        <v>600396</v>
       </c>
       <c r="R8" t="n">
-        <v>6973807</v>
+        <v>6973386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,7 +1524,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1468</t>
+          <t>2024_1467</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1569,7 +1534,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1579,7 +1544,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid myr</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,10 +1569,265 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123434993</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>600451</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6973807</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2024_1468</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>Felix Gunnarsson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123325527</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>600373</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6973646</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2024_1451</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 20695-2025 artfynd.xlsx
+++ b/artfynd/A 20695-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325511</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325529</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325526</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1187,6 +1207,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,6 +1342,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325505</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1447,6 +1477,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1577,6 +1612,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325499</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1702,6 +1742,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123434993</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1832,8 +1877,24 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325527</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>